--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -2998,7 +2998,7 @@
         <v>127735544</v>
       </c>
       <c r="B22" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127735545</v>
       </c>
       <c r="B23" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>127735596</v>
       </c>
       <c r="B24" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>127735542</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127735536</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>127735533</v>
       </c>
       <c r="B27" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127735543</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127735537</v>
       </c>
       <c r="B29" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>127735546</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>127735540</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>127735535</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>127735538</v>
       </c>
       <c r="B33" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>127735541</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -2998,7 +2998,7 @@
         <v>127735544</v>
       </c>
       <c r="B22" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127735545</v>
       </c>
       <c r="B23" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>127735596</v>
       </c>
       <c r="B24" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>127735542</v>
       </c>
       <c r="B25" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127735536</v>
       </c>
       <c r="B26" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>127735533</v>
       </c>
       <c r="B27" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127735543</v>
       </c>
       <c r="B28" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127735537</v>
       </c>
       <c r="B29" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>127735546</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>127735540</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>127735535</v>
       </c>
       <c r="B32" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>127735538</v>
       </c>
       <c r="B33" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>127735541</v>
       </c>
       <c r="B34" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4055,32 +4055,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127735535</v>
+        <v>127735538</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>92654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406013</v>
+        <v>405926</v>
       </c>
       <c r="R32" t="n">
-        <v>6855437</v>
+        <v>6855120</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4161,32 +4161,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127735538</v>
+        <v>127735535</v>
       </c>
       <c r="B33" t="n">
-        <v>92654</v>
+        <v>92636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405926</v>
+        <v>406013</v>
       </c>
       <c r="R33" t="n">
-        <v>6855120</v>
+        <v>6855437</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4371,6 +4371,414 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128340313</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>406080</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6855165</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128340316</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>406078</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6855276</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128340315</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>406145</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6855373</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128340314</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>406066</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6855155</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4055,32 +4055,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127735538</v>
+        <v>127735535</v>
       </c>
       <c r="B32" t="n">
-        <v>92654</v>
+        <v>92636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405926</v>
+        <v>406013</v>
       </c>
       <c r="R32" t="n">
-        <v>6855120</v>
+        <v>6855437</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4161,32 +4161,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127735535</v>
+        <v>127735538</v>
       </c>
       <c r="B33" t="n">
-        <v>92636</v>
+        <v>92654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406013</v>
+        <v>405926</v>
       </c>
       <c r="R33" t="n">
-        <v>6855437</v>
+        <v>6855120</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4055,32 +4055,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127735535</v>
+        <v>127735538</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>92654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406013</v>
+        <v>405926</v>
       </c>
       <c r="R32" t="n">
-        <v>6855437</v>
+        <v>6855120</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4161,32 +4161,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127735538</v>
+        <v>127735535</v>
       </c>
       <c r="B33" t="n">
-        <v>92654</v>
+        <v>92636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405926</v>
+        <v>406013</v>
       </c>
       <c r="R33" t="n">
-        <v>6855120</v>
+        <v>6855437</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -2998,7 +2998,7 @@
         <v>127735544</v>
       </c>
       <c r="B22" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127735545</v>
       </c>
       <c r="B23" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>127735596</v>
       </c>
       <c r="B24" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>127735542</v>
       </c>
       <c r="B25" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127735536</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>127735533</v>
       </c>
       <c r="B27" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127735543</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127735537</v>
       </c>
       <c r="B29" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>127735546</v>
       </c>
       <c r="B30" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>127735540</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4055,32 +4055,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127735538</v>
+        <v>127735535</v>
       </c>
       <c r="B32" t="n">
-        <v>92654</v>
+        <v>92644</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405926</v>
+        <v>406013</v>
       </c>
       <c r="R32" t="n">
-        <v>6855120</v>
+        <v>6855437</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4161,32 +4161,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127735535</v>
+        <v>127735538</v>
       </c>
       <c r="B33" t="n">
-        <v>92636</v>
+        <v>92662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406013</v>
+        <v>405926</v>
       </c>
       <c r="R33" t="n">
-        <v>6855437</v>
+        <v>6855120</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>127735541</v>
       </c>
       <c r="B34" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -2998,7 +2998,7 @@
         <v>127735544</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127735545</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>127735596</v>
       </c>
       <c r="B24" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>127735542</v>
       </c>
       <c r="B25" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127735536</v>
       </c>
       <c r="B26" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>127735533</v>
       </c>
       <c r="B27" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>127735543</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127735537</v>
       </c>
       <c r="B29" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>127735546</v>
       </c>
       <c r="B30" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>127735540</v>
       </c>
       <c r="B31" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>127735535</v>
       </c>
       <c r="B32" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>127735538</v>
       </c>
       <c r="B33" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>127735541</v>
       </c>
       <c r="B34" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4577,32 +4577,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340315</v>
+        <v>128340314</v>
       </c>
       <c r="B37" t="n">
-        <v>92788</v>
+        <v>92794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406145</v>
+        <v>406066</v>
       </c>
       <c r="R37" t="n">
-        <v>6855373</v>
+        <v>6855155</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4679,32 +4679,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128340314</v>
+        <v>128340315</v>
       </c>
       <c r="B38" t="n">
-        <v>92794</v>
+        <v>92788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406066</v>
+        <v>406145</v>
       </c>
       <c r="R38" t="n">
-        <v>6855155</v>
+        <v>6855373</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4577,32 +4577,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128340314</v>
+        <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92794</v>
+        <v>92788</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406066</v>
+        <v>406145</v>
       </c>
       <c r="R37" t="n">
-        <v>6855155</v>
+        <v>6855373</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4679,32 +4679,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128340315</v>
+        <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92788</v>
+        <v>92794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406145</v>
+        <v>406066</v>
       </c>
       <c r="R38" t="n">
-        <v>6855373</v>
+        <v>6855155</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>128340313</v>
       </c>
       <c r="B35" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128340316</v>
       </c>
       <c r="B36" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>128340315</v>
       </c>
       <c r="B37" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>128340314</v>
       </c>
       <c r="B38" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 41755-2025 artfynd.xlsx
+++ b/artfynd/A 41755-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606882</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610453</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149986</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735537</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735548</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735596</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340315</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79948913</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79948926</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2468,6 +2553,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564184</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2672,6 +2767,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610427</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2778,6 +2878,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149981</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149982</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149983</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149987</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149989</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3308,6 +3433,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149990</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3414,6 +3544,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149993</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3520,6 +3655,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735533</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3626,6 +3766,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735536</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3732,6 +3877,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735540</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3838,6 +3988,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735541</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3944,6 +4099,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735543</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4050,6 +4210,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735544</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4156,6 +4321,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735545</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4262,6 +4432,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735546</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4368,6 +4543,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735547</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4470,6 +4650,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340313</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4572,6 +4757,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340314</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4674,6 +4864,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340316</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4785,6 +4980,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79948915</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4891,6 +5091,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735538</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4997,6 +5202,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149991</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5103,6 +5313,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149985</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5209,6 +5424,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149984</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5315,8 +5535,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>